--- a/Dados/2026-05.xlsx
+++ b/Dados/2026-05.xlsx
@@ -5945,7 +5945,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>VATHOR COMÉRCIO DE METAIS LTDA</t>
+          <t>MONTARE INDUSTRIAL LTDA ME</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.9538461538461539</v>
+        <v>0.9882352941176471</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>0.9705882352941176</v>
       </c>
       <c r="E103" t="n">
-        <v>0.9230769230769231</v>
+        <v>1</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -5968,53 +5968,53 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="H103" t="n">
-        <v>12</v>
+        <v>68</v>
       </c>
       <c r="I103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>5733.91</v>
+        <v>23994.63</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Sem ocorrências no período</t>
+          <t>2 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SIMA EMBALAGENS E MADEIRAS LTDA</t>
+          <t>BOLD PARTICIPACOES S.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Arthur Gabriel Dero</t>
+          <t>Edson Carlos Borges</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.9368421052631579</v>
+        <v>0.9777777777777777</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="E104" t="n">
-        <v>0.8947368421052632</v>
+        <v>1</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -6022,53 +6022,53 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H104" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>24906.16</v>
+        <v>13232.24</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Sem ocorrências no período</t>
+          <t>1 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>WECO DO BRASIL QUIMICA LTDA</t>
+          <t>VATHOR COMÉRCIO DE METAIS LTDA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Edson Carlos Borges</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="D105" t="n">
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -6076,16 +6076,16 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H105" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J105" t="n">
-        <v>12047.79</v>
+        <v>5733.91</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -6107,22 +6107,22 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>WEG DRIVES E CONTROLS - AUTOMACAO LTDA</t>
+          <t>SIMA EMBALAGENS E MADEIRAS LTDA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Misael Severino</t>
+          <t>Arthur Gabriel Dero</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>0.9225806451612903</v>
+        <v>0.9368421052631579</v>
       </c>
       <c r="D106" t="n">
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -6130,16 +6130,16 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="H106" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J106" t="n">
-        <v>83958.42999999999</v>
+        <v>24906.16</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -6161,22 +6161,22 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>TASCO LTDA</t>
+          <t>WECO DO BRASIL QUIMICA LTDA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Arthur Gabriel Dero</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>0.9181818181818182</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="D107" t="n">
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -6184,16 +6184,16 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H107" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I107" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J107" t="n">
-        <v>13310.42</v>
+        <v>12047.79</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -6215,22 +6215,22 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IMPORTADORA DE ROLAMENTOS RADIAL LTDA</t>
+          <t>WEG DRIVES E CONTROLS - AUTOMACAO LTDA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Arthur Gabriel Dero</t>
+          <t>Misael Severino</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.9142857142857143</v>
+        <v>0.9225806451612903</v>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -6238,16 +6238,16 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="H108" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J108" t="n">
-        <v>1676.62</v>
+        <v>83958.42999999999</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -6269,39 +6269,39 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SIEMENS BRASIL LTDA.</t>
+          <t>TASCO LTDA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Misael Severino</t>
+          <t>Arthur Gabriel Dero</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0.8956521739130434</v>
+        <v>0.9181818181818182</v>
       </c>
       <c r="D109" t="n">
         <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>0.8260869565217391</v>
+        <v>0.8636363636363636</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>B - BOM</t>
+          <t>A - EXCELENTE</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H109" t="n">
         <v>19</v>
       </c>
       <c r="I109" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J109" t="n">
-        <v>132713.73</v>
+        <v>13310.42</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A.T.I BRASIL ART. TEC. INDS. LTDA</t>
+          <t>IMPORTADORA DE ROLAMENTOS RADIAL LTDA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -6332,30 +6332,30 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>0.8909090909090909</v>
+        <v>0.9142857142857143</v>
       </c>
       <c r="D110" t="n">
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>B - BOM</t>
+          <t>A - EXCELENTE</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H110" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I110" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J110" t="n">
-        <v>46566.81</v>
+        <v>1676.62</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -6377,22 +6377,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ALFA INSTRUMENTOS ELETRONICOS LTDA.</t>
+          <t>MAC LASER INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Edson Carlos Borges</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0.88</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>0.9705882352941176</v>
       </c>
       <c r="E111" t="n">
-        <v>0.8</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -6400,53 +6400,53 @@
         </is>
       </c>
       <c r="G111" t="n">
+        <v>34</v>
+      </c>
+      <c r="H111" t="n">
+        <v>29</v>
+      </c>
+      <c r="I111" t="n">
         <v>5</v>
       </c>
-      <c r="H111" t="n">
-        <v>4</v>
-      </c>
-      <c r="I111" t="n">
-        <v>1</v>
-      </c>
       <c r="J111" t="n">
-        <v>65253.06</v>
+        <v>55503.12</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Sem ocorrências no período</t>
+          <t>1 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DIMAROL COM. DE ROLAM E PC LTDA</t>
+          <t>SIEMENS BRASIL LTDA.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Misael Severino</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.88</v>
+        <v>0.8956521739130434</v>
       </c>
       <c r="D112" t="n">
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>0.8</v>
+        <v>0.8260869565217391</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -6454,16 +6454,16 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="H112" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I112" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J112" t="n">
-        <v>4890.92</v>
+        <v>132713.73</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -6485,22 +6485,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AIRFAG IND. E COM. LTDA</t>
+          <t>A.T.I BRASIL ART. TEC. INDS. LTDA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Edson Carlos Borges</t>
+          <t>Arthur Gabriel Dero</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0.8736842105263158</v>
+        <v>0.8909090909090909</v>
       </c>
       <c r="D113" t="n">
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -6508,16 +6508,16 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H113" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I113" t="n">
         <v>4</v>
       </c>
       <c r="J113" t="n">
-        <v>40255.2</v>
+        <v>46566.81</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -6539,22 +6539,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2F DO BRASIL INDUSTRIA METALURGICA LTDA</t>
+          <t>DIMAROL COM. DE ROLAM E PC LTDA</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Edson Carlos Borges</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>0.8615384615384616</v>
+        <v>0.88</v>
       </c>
       <c r="D114" t="n">
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -6562,16 +6562,16 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="H114" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="I114" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
-        <v>33054.1</v>
+        <v>4890.92</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CAROL COML CATARINENSE ROL LTDA</t>
+          <t>ALFA INSTRUMENTOS ELETRONICOS LTDA.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -6602,13 +6602,13 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="D115" t="n">
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -6616,16 +6616,16 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H115" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J115" t="n">
-        <v>3153.87</v>
+        <v>65253.06</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -6647,22 +6647,22 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>JEAN CARLOS DE ARAUJO - ME</t>
+          <t>AIRFAG IND. E COM. LTDA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Edson Carlos Borges</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8736842105263158</v>
       </c>
       <c r="D116" t="n">
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6825396825396826</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -6670,16 +6670,16 @@
         </is>
       </c>
       <c r="G116" t="n">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="H116" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="I116" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="J116" t="n">
-        <v>16886.75</v>
+        <v>40255.2</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -6694,29 +6694,29 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>20 de 63 entregas atrasadas</t>
+          <t>Sem ocorrências no período</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ESTATEC IND. E COM. LTDA</t>
+          <t>2F DO BRASIL INDUSTRIA METALURGICA LTDA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Edson Carlos Borges</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0.8</v>
+        <v>0.8615384615384616</v>
       </c>
       <c r="D117" t="n">
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -6724,16 +6724,16 @@
         </is>
       </c>
       <c r="G117" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="H117" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="I117" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="J117" t="n">
-        <v>10594.08</v>
+        <v>33054.1</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -6748,29 +6748,29 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>1 de 3 entregas atrasadas</t>
+          <t>Sem ocorrências no período</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>GRIFFUS PCB INDUSTRIA E COMERCIO EIRELLI</t>
+          <t>CAROL COML CATARINENSE ROL LTDA</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Misael Severino</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="D118" t="n">
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.75</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -6778,16 +6778,16 @@
         </is>
       </c>
       <c r="G118" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H118" t="n">
+        <v>6</v>
+      </c>
+      <c r="I118" t="n">
         <v>2</v>
       </c>
-      <c r="I118" t="n">
-        <v>1</v>
-      </c>
       <c r="J118" t="n">
-        <v>6887.360000000001</v>
+        <v>3153.87</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -6802,29 +6802,29 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>1 de 3 entregas atrasadas</t>
+          <t>Sem ocorrências no período</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>INECEL ESTRUTURAS ELETRICAS LTDA</t>
+          <t>ACOPAR COM. DE PARAFUSOS LTDA</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Alex Sandro Jung</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>0.8</v>
+        <v>0.827027027027027</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>0.972972972972973</v>
       </c>
       <c r="E119" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -6832,53 +6832,53 @@
         </is>
       </c>
       <c r="G119" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H119" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J119" t="n">
-        <v>55762.75</v>
+        <v>9947.01</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>1 de 3 entregas atrasadas</t>
+          <t>1 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>JOSE ADRIANO COMERCIO ATACADISTA E VAREJ</t>
+          <t>KL POX PINTURA ELETROSTATICA LTDA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Nithael Alexandre Krepsky Silveira</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.8</v>
+        <v>0.8186788154897495</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0.9908883826879271</v>
       </c>
       <c r="E120" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.7038724373576309</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -6886,53 +6886,53 @@
         </is>
       </c>
       <c r="G120" t="n">
-        <v>6</v>
+        <v>439</v>
       </c>
       <c r="H120" t="n">
+        <v>309</v>
+      </c>
+      <c r="I120" t="n">
+        <v>130</v>
+      </c>
+      <c r="J120" t="n">
+        <v>40767.64</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
         <v>4</v>
       </c>
-      <c r="I120" t="n">
-        <v>2</v>
-      </c>
-      <c r="J120" t="n">
-        <v>2605.4</v>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L120" t="n">
-        <v>0</v>
-      </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2 de 6 entregas atrasadas</t>
+          <t>4 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>KEUNECKE FERRAGENS E FECHADURAS LTDA.</t>
+          <t>JEAN CARLOS DE ARAUJO - ME</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Misael Severino</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>0.8</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6825396825396826</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -6940,16 +6940,16 @@
         </is>
       </c>
       <c r="G121" t="n">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="H121" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="I121" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J121" t="n">
-        <v>1975.34</v>
+        <v>16886.75</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -6964,19 +6964,19 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>1 de 3 entregas atrasadas</t>
+          <t>20 de 63 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ARSYSTEM FERRAMENTAS &amp; EQUIPAMENTOS LTDA</t>
+          <t>ACZ INOX COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Edson Carlos Borges</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -7003,7 +7003,7 @@
         <v>1</v>
       </c>
       <c r="J122" t="n">
-        <v>3614</v>
+        <v>42224.29</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -7025,22 +7025,22 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ACZ INOX COMERCIAL LTDA</t>
+          <t>SIPAR FERRAMENTAS LTDA</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Alex Sandro Jung</t>
         </is>
       </c>
       <c r="C123" t="n">
         <v>0.8</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="E123" t="n">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -7048,70 +7048,70 @@
         </is>
       </c>
       <c r="G123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H123" t="n">
         <v>2</v>
       </c>
       <c r="I123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123" t="n">
-        <v>42224.29</v>
+        <v>745.5300000000001</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>1 de 3 entregas atrasadas</t>
+          <t>1 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CRV INDUSTRIAL COM DE FIX LTDA</t>
+          <t>KEUNECKE FERRAGENS E FECHADURAS LTDA.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Alex Sandro Jung</t>
+          <t>Misael Severino</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>0.775</v>
+        <v>0.8</v>
       </c>
       <c r="D124" t="n">
         <v>1</v>
       </c>
       <c r="E124" t="n">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>C - REGULAR</t>
+          <t>B - BOM</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="H124" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I124" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J124" t="n">
-        <v>7386.69</v>
+        <v>1975.34</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -7126,46 +7126,46 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>9 de 24 entregas atrasadas</t>
+          <t>1 de 3 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SANTEC JATEAMENTO E PINTURA LTDA</t>
+          <t>JOSE ADRIANO COMERCIO ATACADISTA E VAREJ</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Nithael Alexandre Krepsky Silveira</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.7683397683397684</v>
+        <v>0.8</v>
       </c>
       <c r="D125" t="n">
         <v>1</v>
       </c>
       <c r="E125" t="n">
-        <v>0.6138996138996139</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>C - REGULAR</t>
+          <t>B - BOM</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>259</v>
+        <v>6</v>
       </c>
       <c r="H125" t="n">
-        <v>159</v>
+        <v>4</v>
       </c>
       <c r="I125" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="J125" t="n">
-        <v>14035.23</v>
+        <v>2605.4</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
@@ -7180,46 +7180,46 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>100 de 259 entregas atrasadas</t>
+          <t>2 de 6 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>JUNKES E SCHIESTL IMPRESSÃO DIGITAL LTDA</t>
+          <t>GRIFFUS PCB INDUSTRIA E COMERCIO EIRELLI</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Misael Severino</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="D126" t="n">
         <v>1</v>
       </c>
       <c r="E126" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>C - REGULAR</t>
+          <t>B - BOM</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J126" t="n">
-        <v>2157.48</v>
+        <v>6887.360000000001</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
@@ -7234,46 +7234,46 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2 de 5 entregas atrasadas</t>
+          <t>1 de 3 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>METALURGICA ADENOX LTDA</t>
+          <t>INECEL ESTRUTURAS ELETRICAS LTDA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Nithael Alexandre Krepsky Silveira</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="D127" t="n">
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>C - REGULAR</t>
+          <t>B - BOM</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H127" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J127" t="n">
-        <v>6700</v>
+        <v>55762.75</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
@@ -7288,14 +7288,14 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2 de 5 entregas atrasadas</t>
+          <t>1 de 3 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>X LASER EXCELENCIA EM CORTE E DOBRA DE M</t>
+          <t>ARSYSTEM FERRAMENTAS &amp; EQUIPAMENTOS LTDA</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -7304,30 +7304,30 @@
         </is>
       </c>
       <c r="C128" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="D128" t="n">
         <v>1</v>
       </c>
       <c r="E128" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>C - REGULAR</t>
+          <t>B - BOM</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H128" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J128" t="n">
-        <v>3344.72</v>
+        <v>3614</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
@@ -7342,46 +7342,46 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2 de 5 entregas atrasadas</t>
+          <t>1 de 3 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>PAFER COMERCIAL LTDA</t>
+          <t>ESTATEC IND. E COM. LTDA</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Alex Sandro Jung</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>0.7375</v>
+        <v>0.8</v>
       </c>
       <c r="D129" t="n">
         <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>0.5625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>C - REGULAR</t>
+          <t>B - BOM</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="H129" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I129" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J129" t="n">
-        <v>4117.04</v>
+        <v>10594.08</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
@@ -7396,29 +7396,29 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>7 de 16 entregas atrasadas</t>
+          <t>1 de 3 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>KAIROS INDUSTRIA MECANICA EIRELI - EPP</t>
+          <t>CRV INDUSTRIAL COM DE FIX LTDA</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Jair Wermuth</t>
+          <t>Alex Sandro Jung</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0.7367159971811135</v>
+        <v>0.775</v>
       </c>
       <c r="D130" t="n">
-        <v>0.9696969696969697</v>
+        <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>0.5813953488372093</v>
+        <v>0.625</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -7426,53 +7426,53 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H130" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I130" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="J130" t="n">
-        <v>21099.36</v>
+        <v>7386.69</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>18 de 43 entregas atrasadas · 2 não conformidade(s)</t>
+          <t>9 de 24 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>REWE MATERIAIS DE CONSTRUCAO LTDA</t>
+          <t>SANTEC JATEAMENTO E PINTURA LTDA</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Alex Sandro Jung</t>
+          <t>Nithael Alexandre Krepsky Silveira</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>0.7</v>
+        <v>0.7683397683397684</v>
       </c>
       <c r="D131" t="n">
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>0.5</v>
+        <v>0.6138996138996139</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -7480,16 +7480,16 @@
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>259</v>
       </c>
       <c r="H131" t="n">
-        <v>1</v>
+        <v>159</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="J131" t="n">
-        <v>198</v>
+        <v>14035.23</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
@@ -7504,14 +7504,14 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>1 de 2 entregas atrasadas</t>
+          <t>100 de 259 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>IBRAM IND. BRASIL DE MAQS. LTDA.</t>
+          <t>JUNKES E SCHIESTL IMPRESSÃO DIGITAL LTDA</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -7520,13 +7520,13 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="D132" t="n">
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -7534,16 +7534,16 @@
         </is>
       </c>
       <c r="G132" t="n">
+        <v>5</v>
+      </c>
+      <c r="H132" t="n">
+        <v>3</v>
+      </c>
+      <c r="I132" t="n">
         <v>2</v>
       </c>
-      <c r="H132" t="n">
-        <v>1</v>
-      </c>
-      <c r="I132" t="n">
-        <v>1</v>
-      </c>
       <c r="J132" t="n">
-        <v>7245</v>
+        <v>2157.48</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
@@ -7558,29 +7558,29 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>1 de 2 entregas atrasadas</t>
+          <t>2 de 5 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>STECK INDUSTRIA ELETRICA LTDA</t>
+          <t>X LASER EXCELENCIA EM CORTE E DOBRA DE M</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Edson Carlos Borges</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="D133" t="n">
         <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -7588,16 +7588,16 @@
         </is>
       </c>
       <c r="G133" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H133" t="n">
         <v>3</v>
       </c>
       <c r="I133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J133" t="n">
-        <v>6893.85</v>
+        <v>3344.72</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
@@ -7612,29 +7612,29 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>3 de 6 entregas atrasadas</t>
+          <t>2 de 5 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>DNCM INDUSTRIA E COMERCIO LTDA</t>
+          <t>METALURGICA ADENOX LTDA</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Nithael Alexandre Krepsky Silveira</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="D134" t="n">
         <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -7642,16 +7642,16 @@
         </is>
       </c>
       <c r="G134" t="n">
+        <v>5</v>
+      </c>
+      <c r="H134" t="n">
+        <v>3</v>
+      </c>
+      <c r="I134" t="n">
         <v>2</v>
       </c>
-      <c r="H134" t="n">
-        <v>1</v>
-      </c>
-      <c r="I134" t="n">
-        <v>1</v>
-      </c>
       <c r="J134" t="n">
-        <v>5980</v>
+        <v>6700</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
@@ -7666,29 +7666,29 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>1 de 2 entregas atrasadas</t>
+          <t>2 de 5 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ELETRISOL IND E COM LTDA</t>
+          <t>PAFER COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Jair Wermuth</t>
+          <t>Alex Sandro Jung</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>0.7</v>
+        <v>0.7375</v>
       </c>
       <c r="D135" t="n">
         <v>1</v>
       </c>
       <c r="E135" t="n">
-        <v>0.5</v>
+        <v>0.5625</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -7696,16 +7696,16 @@
         </is>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="H135" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I135" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J135" t="n">
-        <v>3104.55</v>
+        <v>4117.04</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
@@ -7720,68 +7720,68 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>1 de 2 entregas atrasadas</t>
+          <t>7 de 16 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ALZINOX IND E COM DE MAQ LTDA-ME</t>
+          <t>KAIROS INDUSTRIA MECANICA EIRELI - EPP</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Edson Carlos Borges</t>
+          <t>Jair Wermuth</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0.6727272727272727</v>
+        <v>0.7302325581395349</v>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>0.9534883720930233</v>
       </c>
       <c r="E136" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5813953488372093</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>D - ATENCAO</t>
+          <t>C - REGULAR</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="H136" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I136" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="J136" t="n">
-        <v>15194</v>
+        <v>21099.36</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M136" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>6 de 11 entregas atrasadas</t>
+          <t>18 de 43 entregas atrasadas · 2 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>COBRA CORRENTES BRASILEIRAS LTDA</t>
+          <t>DNCM INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -7790,30 +7790,30 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.6727272727272727</v>
+        <v>0.7</v>
       </c>
       <c r="D137" t="n">
         <v>1</v>
       </c>
       <c r="E137" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>D - ATENCAO</t>
+          <t>C - REGULAR</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H137" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I137" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J137" t="n">
-        <v>12821.15</v>
+        <v>5980</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
@@ -7828,14 +7828,14 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>6 de 11 entregas atrasadas</t>
+          <t>1 de 2 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>POLISTAMP IND. E COM. LTDA - EPP</t>
+          <t>IBRAM IND. BRASIL DE MAQS. LTDA.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -7844,30 +7844,30 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.7</v>
       </c>
       <c r="D138" t="n">
         <v>1</v>
       </c>
       <c r="E138" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>D - ATENCAO</t>
+          <t>C - REGULAR</t>
         </is>
       </c>
       <c r="G138" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H138" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J138" t="n">
-        <v>3585.34</v>
+        <v>7245</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
@@ -7882,100 +7882,100 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>5 de 9 entregas atrasadas</t>
+          <t>1 de 2 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ENDER USINAGEM LTDA</t>
+          <t>STECK INDUSTRIA ELETRICA LTDA</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Jair Wermuth</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.6488505747126436</v>
+        <v>0.7</v>
       </c>
       <c r="D139" t="n">
-        <v>0.9137931034482758</v>
+        <v>1</v>
       </c>
       <c r="E139" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.5</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>D - ATENCAO</t>
+          <t>C - REGULAR</t>
         </is>
       </c>
       <c r="G139" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="H139" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I139" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="J139" t="n">
-        <v>50356.45</v>
+        <v>6893.85</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>19 de 36 entregas atrasadas · 5 não conformidade(s)</t>
+          <t>3 de 6 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TECNOBELT IND COM DE CORREIAS LTDA EPP</t>
+          <t>REWE MATERIAIS DE CONSTRUCAO LTDA</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Alex Sandro Jung</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="D140" t="n">
         <v>1</v>
       </c>
       <c r="E140" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>D - ATENCAO</t>
+          <t>C - REGULAR</t>
         </is>
       </c>
       <c r="G140" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H140" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I140" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J140" t="n">
-        <v>4812.72</v>
+        <v>198</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
@@ -7990,46 +7990,46 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>9 de 15 entregas atrasadas</t>
+          <t>1 de 2 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>CENTERROL INDÚSTRIA E COMÉRCIO LTDA</t>
+          <t>ELETRISOL IND E COM LTDA</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Jair Wermuth</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="D141" t="n">
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>D - ATENCAO</t>
+          <t>C - REGULAR</t>
         </is>
       </c>
       <c r="G141" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J141" t="n">
-        <v>796.85</v>
+        <v>3104.55</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
@@ -8040,33 +8040,33 @@
         <v>0</v>
       </c>
       <c r="M141" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>3 de 5 entregas atrasadas</t>
+          <t>1 de 2 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>JAV AUTOMACAO INDUSTRIAL LTDA</t>
+          <t>ALZINOX IND E COM DE MAQ LTDA-ME</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Edson Carlos Borges</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.6307692307692307</v>
+        <v>0.6727272727272727</v>
       </c>
       <c r="D142" t="n">
         <v>1</v>
       </c>
       <c r="E142" t="n">
-        <v>0.3846153846153846</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -8074,16 +8074,16 @@
         </is>
       </c>
       <c r="G142" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H142" t="n">
         <v>5</v>
       </c>
       <c r="I142" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J142" t="n">
-        <v>34081.48</v>
+        <v>15194</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
@@ -8098,29 +8098,29 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>8 de 13 entregas atrasadas</t>
+          <t>6 de 11 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>BARTH USINAGEM LTDA-ME</t>
+          <t>COBRA CORRENTES BRASILEIRAS LTDA</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Jair Wermuth</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.6193770589997005</v>
+        <v>0.6727272727272727</v>
       </c>
       <c r="D143" t="n">
-        <v>0.9682539682539683</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>0.3867924528301887</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -8128,53 +8128,53 @@
         </is>
       </c>
       <c r="G143" t="n">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="H143" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="I143" t="n">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="J143" t="n">
-        <v>44213.44</v>
+        <v>12821.15</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M143" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>65 de 106 entregas atrasadas · 4 não conformidade(s)</t>
+          <t>6 de 11 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>KEYENCE BRASIL COMERCIO DE PRODUTOS ELE</t>
+          <t>POLISTAMP IND. E COM. LTDA - EPP</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>(sem entrega no mês)</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -8182,53 +8182,53 @@
         </is>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H144" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J144" t="n">
-        <v>0</v>
+        <v>3585.34</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>1 não conformidade(s)</t>
+          <t>5 de 9 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MONTARE INDUSTRIAL LTDA ME</t>
+          <t>CENTERROL INDÚSTRIA E COMÉRCIO LTDA</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Edson Carlos Borges</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="D145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -8236,38 +8236,38 @@
         </is>
       </c>
       <c r="G145" t="n">
-        <v>68</v>
+        <v>5</v>
       </c>
       <c r="H145" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J145" t="n">
-        <v>23994.63</v>
+        <v>796.85</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M145" t="n">
         <v>2</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2 não conformidade(s)</t>
+          <t>3 de 5 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SAGATOR COMERCIO DE GAS LTDA ME</t>
+          <t>TECNOBELT IND COM DE CORREIAS LTDA EPP</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -8276,13 +8276,13 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="D146" t="n">
         <v>1</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -8290,16 +8290,16 @@
         </is>
       </c>
       <c r="G146" t="n">
+        <v>15</v>
+      </c>
+      <c r="H146" t="n">
+        <v>6</v>
+      </c>
+      <c r="I146" t="n">
         <v>9</v>
       </c>
-      <c r="H146" t="n">
-        <v>3</v>
-      </c>
-      <c r="I146" t="n">
-        <v>6</v>
-      </c>
       <c r="J146" t="n">
-        <v>2925</v>
+        <v>4812.72</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
@@ -8314,29 +8314,29 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>6 de 9 entregas atrasadas</t>
+          <t>9 de 15 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SIPAR FERRAMENTAS LTDA</t>
+          <t>JAV AUTOMACAO INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Alex Sandro Jung</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>0.6</v>
+        <v>0.6307692307692307</v>
       </c>
       <c r="D147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E147" t="n">
-        <v>1</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -8344,53 +8344,53 @@
         </is>
       </c>
       <c r="G147" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H147" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I147" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J147" t="n">
-        <v>745.5300000000001</v>
+        <v>34081.48</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>1 não conformidade(s)</t>
+          <t>8 de 13 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>TELAS BR FENCE LTDA</t>
+          <t>ENDER USINAGEM LTDA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Jair Wermuth</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0.6</v>
+        <v>0.6277777777777778</v>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>0.8611111111111112</v>
       </c>
       <c r="E148" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4722222222222222</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -8398,53 +8398,53 @@
         </is>
       </c>
       <c r="G148" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="H148" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="I148" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J148" t="n">
-        <v>30194.5</v>
+        <v>50356.45</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M148" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2 de 3 entregas atrasadas</t>
+          <t>19 de 36 entregas atrasadas · 5 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ROLETES BRASIL COMERCIAL LTDA</t>
+          <t>SMC AUTOMACAO DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Misael Severino</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.6</v>
+        <v>0.6265232974910394</v>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>0.996415770609319</v>
       </c>
       <c r="E149" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3799283154121864</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -8452,53 +8452,53 @@
         </is>
       </c>
       <c r="G149" t="n">
-        <v>3</v>
+        <v>279</v>
       </c>
       <c r="H149" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>173</v>
       </c>
       <c r="J149" t="n">
-        <v>5120.299999999999</v>
+        <v>104019.34</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2 de 3 entregas atrasadas</t>
+          <t>173 de 279 entregas atrasadas · 1 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>AIR LIQUIDE BRASIL LTDA</t>
+          <t>BARTH USINAGEM LTDA-ME</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Jair Wermuth</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>0.6</v>
+        <v>0.6169811320754717</v>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>0.9622641509433962</v>
       </c>
       <c r="E150" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3867924528301887</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -8506,53 +8506,53 @@
         </is>
       </c>
       <c r="G150" t="n">
-        <v>15</v>
+        <v>106</v>
       </c>
       <c r="H150" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="I150" t="n">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="J150" t="n">
-        <v>5645.06</v>
+        <v>44213.44</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M150" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>10 de 15 entregas atrasadas</t>
+          <t>65 de 106 entregas atrasadas · 4 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FINDER COMPONENTES LTDA</t>
+          <t>PRENSA IND. COM. DE PECAS LTDA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Misael Severino</t>
+          <t>Edson Carlos Borges</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.6</v>
+        <v>0.6111111111111112</v>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>0.9444444444444444</v>
       </c>
       <c r="E151" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -8560,53 +8560,53 @@
         </is>
       </c>
       <c r="G151" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="H151" t="n">
+        <v>7</v>
+      </c>
+      <c r="I151" t="n">
+        <v>11</v>
+      </c>
+      <c r="J151" t="n">
+        <v>49795.06</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>1</v>
+      </c>
+      <c r="M151" t="n">
         <v>3</v>
       </c>
-      <c r="I151" t="n">
-        <v>6</v>
-      </c>
-      <c r="J151" t="n">
-        <v>30710.6</v>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>NÃO</t>
-        </is>
-      </c>
-      <c r="L151" t="n">
-        <v>0</v>
-      </c>
-      <c r="M151" t="n">
-        <v>0</v>
-      </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>6 de 9 entregas atrasadas</t>
+          <t>11 de 18 entregas atrasadas · 1 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>BOLD PARTICIPACOES S.A.</t>
+          <t>FINDER COMPONENTES LTDA</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Edson Carlos Borges</t>
+          <t>Misael Severino</t>
         </is>
       </c>
       <c r="C152" t="n">
         <v>0.6</v>
       </c>
       <c r="D152" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>1</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -8614,70 +8614,70 @@
         </is>
       </c>
       <c r="G152" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="H152" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J152" t="n">
-        <v>13232.24</v>
+        <v>30710.6</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>1 não conformidade(s)</t>
+          <t>6 de 9 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CND REVESTIMENTOS INDUSTRIAIS LTDA</t>
+          <t>AIR LIQUIDE BRASIL LTDA</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Nithael Alexandre Krepsky Silveira</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.6</v>
       </c>
       <c r="D153" t="n">
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>E - CRITICO</t>
+          <t>D - ATENCAO</t>
         </is>
       </c>
       <c r="G153" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="H153" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I153" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J153" t="n">
-        <v>5960.92</v>
+        <v>5645.06</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
@@ -8692,46 +8692,46 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>5 de 7 entregas atrasadas</t>
+          <t>10 de 15 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>GALRIO GALVANOSTEGIA TECNICA LTDA</t>
+          <t>ROLETES BRASIL COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Nithael Alexandre Krepsky Silveira</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>0.5629310344827586</v>
+        <v>0.6</v>
       </c>
       <c r="D154" t="n">
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>0.271551724137931</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>E - CRITICO</t>
+          <t>D - ATENCAO</t>
         </is>
       </c>
       <c r="G154" t="n">
-        <v>232</v>
+        <v>3</v>
       </c>
       <c r="H154" t="n">
-        <v>63</v>
+        <v>1</v>
       </c>
       <c r="I154" t="n">
-        <v>169</v>
+        <v>2</v>
       </c>
       <c r="J154" t="n">
-        <v>7942.39</v>
+        <v>5120.299999999999</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
@@ -8746,46 +8746,46 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>169 de 232 entregas atrasadas</t>
+          <t>2 de 3 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>HR USINAGEM LTDA - EPP</t>
+          <t>TELAS BR FENCE LTDA</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Jair Wermuth</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>0.5615384615384615</v>
+        <v>0.6</v>
       </c>
       <c r="D155" t="n">
         <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>0.2692307692307692</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>E - CRITICO</t>
+          <t>D - ATENCAO</t>
         </is>
       </c>
       <c r="G155" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="H155" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I155" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="J155" t="n">
-        <v>43803.7</v>
+        <v>30194.5</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
@@ -8796,195 +8796,195 @@
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>19 de 26 entregas atrasadas</t>
+          <t>2 de 3 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MS APOIO OPERACIONAL LTDA ME</t>
+          <t>KEYENCE BRASIL COMERCIO DE PRODUTOS ELE</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Edson Carlos Borges</t>
+          <t>(sem entrega no mês)</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E156" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>E - CRITICO</t>
+          <t>D - ATENCAO</t>
         </is>
       </c>
       <c r="G156" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I156" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J156" t="n">
-        <v>18305.65</v>
+        <v>0</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>3 de 4 entregas atrasadas</t>
+          <t>1 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>METALTEC STEEL HOME LTDA</t>
+          <t>SAGATOR COMERCIO DE GAS LTDA ME</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Jair Wermuth</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>0.5234983664237246</v>
+        <v>0.6</v>
       </c>
       <c r="D157" t="n">
-        <v>0.9826589595375722</v>
+        <v>1</v>
       </c>
       <c r="E157" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>E - CRITICO</t>
+          <t>D - ATENCAO</t>
         </is>
       </c>
       <c r="G157" t="n">
-        <v>161</v>
+        <v>9</v>
       </c>
       <c r="H157" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="I157" t="n">
-        <v>126</v>
+        <v>6</v>
       </c>
       <c r="J157" t="n">
-        <v>128893.42</v>
+        <v>2925</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M157" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>126 de 161 entregas atrasadas · 3 não conformidade(s)</t>
+          <t>6 de 9 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>NITSCHE ENGRENAGENS INDUST. E COM. LTDA</t>
+          <t>WEG EQUIPTOS ELETRICOS S/A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Jair Wermuth</t>
+          <t>Misael Severino</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="E158" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>E - CRITICO</t>
+          <t>D - ATENCAO</t>
         </is>
       </c>
       <c r="G158" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H158" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I158" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="J158" t="n">
-        <v>35970.78</v>
+        <v>32960.32</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M158" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>16 de 20 entregas atrasadas</t>
+          <t>2 de 5 entregas atrasadas · 2 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MAC LASER INDUSTRIAL LTDA</t>
+          <t>CND REVESTIMENTOS INDUSTRIAIS LTDA</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Edson Carlos Borges</t>
+          <t>Nithael Alexandre Krepsky Silveira</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>0.5117647058823529</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E159" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -8992,53 +8992,53 @@
         </is>
       </c>
       <c r="G159" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="H159" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="I159" t="n">
         <v>5</v>
       </c>
       <c r="J159" t="n">
-        <v>55503.12</v>
+        <v>5960.92</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>1 não conformidade(s)</t>
+          <t>5 de 7 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PRENSA IND. COM. DE PECAS LTDA</t>
+          <t>GALRIO GALVANOSTEGIA TECNICA LTDA</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Edson Carlos Borges</t>
+          <t>Nithael Alexandre Krepsky Silveira</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>0.5</v>
+        <v>0.5629310344827586</v>
       </c>
       <c r="D160" t="n">
-        <v>0.6666666666666667</v>
+        <v>1</v>
       </c>
       <c r="E160" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.271551724137931</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -9046,38 +9046,38 @@
         </is>
       </c>
       <c r="G160" t="n">
-        <v>18</v>
+        <v>232</v>
       </c>
       <c r="H160" t="n">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="I160" t="n">
-        <v>11</v>
+        <v>169</v>
       </c>
       <c r="J160" t="n">
-        <v>49795.06</v>
+        <v>7942.39</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M160" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>11 de 18 entregas atrasadas · 1 não conformidade(s)</t>
+          <t>169 de 232 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SIEBEN USINAGEM LTDA</t>
+          <t>HR USINAGEM LTDA - EPP</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -9086,13 +9086,13 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>0.46</v>
+        <v>0.5615384615384615</v>
       </c>
       <c r="D161" t="n">
         <v>1</v>
       </c>
       <c r="E161" t="n">
-        <v>0.1</v>
+        <v>0.2692307692307692</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -9100,16 +9100,16 @@
         </is>
       </c>
       <c r="G161" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="H161" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I161" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J161" t="n">
-        <v>8930.200000000001</v>
+        <v>43803.7</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -9120,33 +9120,33 @@
         <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>18 de 20 entregas atrasadas</t>
+          <t>19 de 26 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MTJ USINAGEM EIRELI</t>
+          <t>MS APOIO OPERACIONAL LTDA ME</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Jair Wermuth</t>
+          <t>Edson Carlos Borges</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>0.4468944099378882</v>
+        <v>0.55</v>
       </c>
       <c r="D162" t="n">
-        <v>0.9565217391304348</v>
+        <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>0.1071428571428571</v>
+        <v>0.25</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -9154,53 +9154,53 @@
         </is>
       </c>
       <c r="G162" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="H162" t="n">
+        <v>1</v>
+      </c>
+      <c r="I162" t="n">
         <v>3</v>
       </c>
-      <c r="I162" t="n">
-        <v>25</v>
-      </c>
       <c r="J162" t="n">
-        <v>15810.27</v>
+        <v>18305.65</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M162" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>25 de 28 entregas atrasadas · 2 não conformidade(s)</t>
+          <t>3 de 4 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ACOPAR COM. DE PARAFUSOS LTDA</t>
+          <t>SEW-EURODRIVE BRASIL LTDA</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Alex Sandro Jung</t>
+          <t>Misael Severino</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>0.4378378378378378</v>
+        <v>0.5238095238095237</v>
       </c>
       <c r="D163" t="n">
-        <v>0</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="E163" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -9208,16 +9208,16 @@
         </is>
       </c>
       <c r="G163" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="H163" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="I163" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J163" t="n">
-        <v>9947.01</v>
+        <v>77989.71000000001</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -9232,29 +9232,29 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>1 não conformidade(s)</t>
+          <t>16 de 21 entregas atrasadas · 1 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>KL POX PINTURA ELETROSTATICA LTDA</t>
+          <t>METALTEC STEEL HOME LTDA</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Nithael Alexandre Krepsky Silveira</t>
+          <t>Jair Wermuth</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>0.4223234624145786</v>
+        <v>0.5229813664596273</v>
       </c>
       <c r="D164" t="n">
-        <v>0</v>
+        <v>0.9813664596273292</v>
       </c>
       <c r="E164" t="n">
-        <v>0.7038724373576309</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -9262,16 +9262,16 @@
         </is>
       </c>
       <c r="G164" t="n">
-        <v>439</v>
+        <v>161</v>
       </c>
       <c r="H164" t="n">
-        <v>309</v>
+        <v>35</v>
       </c>
       <c r="I164" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J164" t="n">
-        <v>40767.64</v>
+        <v>128893.42</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
@@ -9279,36 +9279,36 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M164" t="n">
-        <v>4</v>
+        <v>173</v>
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>4 não conformidade(s)</t>
+          <t>126 de 161 entregas atrasadas · 3 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>IGUS DO BRASIL LTDA</t>
+          <t>NITSCHE ENGRENAGENS INDUST. E COM. LTDA</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Misael Severino</t>
+          <t>Jair Wermuth</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>0.4139534883720931</v>
+        <v>0.52</v>
       </c>
       <c r="D165" t="n">
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>0.02325581395348837</v>
+        <v>0.2</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -9316,16 +9316,16 @@
         </is>
       </c>
       <c r="G165" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="H165" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I165" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="J165" t="n">
-        <v>24647.57</v>
+        <v>35970.78</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
@@ -9336,33 +9336,33 @@
         <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>42 de 43 entregas atrasadas</t>
+          <t>16 de 20 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>BLUPEL COM. DE COMPONENTES ELETRONICOS</t>
+          <t>SIEBEN USINAGEM LTDA</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Misael Severino</t>
+          <t>Jair Wermuth</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="D166" t="n">
         <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -9370,16 +9370,16 @@
         </is>
       </c>
       <c r="G166" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I166" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J166" t="n">
-        <v>214.55</v>
+        <v>8930.200000000001</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
@@ -9390,33 +9390,33 @@
         <v>0</v>
       </c>
       <c r="M166" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>1 de 1 entregas atrasadas</t>
+          <t>18 de 20 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BLU SOLDAS FERRAMENTAS LTDA.ME</t>
+          <t>MTJ USINAGEM EIRELI</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Edson Carlos Borges</t>
+          <t>Jair Wermuth</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>0.4</v>
+        <v>0.4357142857142857</v>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -9424,53 +9424,53 @@
         </is>
       </c>
       <c r="G167" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="H167" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I167" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="J167" t="n">
-        <v>139.8</v>
+        <v>15810.27</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M167" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>1 de 1 entregas atrasadas</t>
+          <t>25 de 28 entregas atrasadas · 2 não conformidade(s)</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>DIFF COMÉRCIO DE PAPÉIS E EMBALAGENS LTD</t>
+          <t>IGUS DO BRASIL LTDA</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Misael Severino</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>0.4</v>
+        <v>0.4139534883720931</v>
       </c>
       <c r="D168" t="n">
         <v>1</v>
       </c>
       <c r="E168" t="n">
-        <v>0</v>
+        <v>0.02325581395348837</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -9478,16 +9478,16 @@
         </is>
       </c>
       <c r="G168" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="H168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="J168" t="n">
-        <v>400</v>
+        <v>24647.57</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
@@ -9502,19 +9502,19 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2 de 2 entregas atrasadas</t>
+          <t>42 de 43 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>BIGFER-INDUSTRIA E COMERCIO DE FERRAGENS LTDA</t>
+          <t>BLU SOLDAS FERRAMENTAS LTDA.ME</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Edson Carlos Borges</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -9541,7 +9541,7 @@
         <v>1</v>
       </c>
       <c r="J169" t="n">
-        <v>6375.6</v>
+        <v>139.8</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>MALTA RIO INDUSTRIAL LTDA</t>
+          <t>DIFF COMÉRCIO DE PAPÉIS E EMBALAGENS LTD</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -9910,16 +9910,16 @@
         </is>
       </c>
       <c r="G176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
       </c>
       <c r="I176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J176" t="n">
-        <v>12875.28</v>
+        <v>400</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -9934,14 +9934,14 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>1 de 1 entregas atrasadas</t>
+          <t>2 de 2 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>KAP COMPONENTES ELETRICOS LTDA.</t>
+          <t>BIGFER-INDUSTRIA E COMERCIO DE FERRAGENS LTDA</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -9973,7 +9973,7 @@
         <v>1</v>
       </c>
       <c r="J177" t="n">
-        <v>1078.58</v>
+        <v>6375.6</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>INCAVEL ONIBUS E PECAS LTDA</t>
+          <t>BLUPEL COM. DE COMPONENTES ELETRONICOS</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -10027,7 +10027,7 @@
         <v>1</v>
       </c>
       <c r="J178" t="n">
-        <v>6700</v>
+        <v>214.55</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -10103,12 +10103,12 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>LAPP BRASIL LTDA</t>
+          <t>INCAVEL ONIBUS E PECAS LTDA</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Misael Severino</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -10126,16 +10126,16 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
       </c>
       <c r="I180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J180" t="n">
-        <v>25303.75</v>
+        <v>6700</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>3 de 3 entregas atrasadas</t>
+          <t>1 de 1 entregas atrasadas</t>
         </is>
       </c>
     </row>
@@ -10427,7 +10427,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>VEDAX COMERCIAL LTDA.</t>
+          <t>MALTA RIO INDUSTRIAL LTDA</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -10450,16 +10450,16 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
       </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J186" t="n">
-        <v>390.08</v>
+        <v>12875.28</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -10474,14 +10474,14 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2 de 2 entregas atrasadas</t>
+          <t>1 de 1 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SCHNEIDER ELECTRIC BRASIL LTDA</t>
+          <t>KAP COMPONENTES ELETRICOS LTDA.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -10513,7 +10513,7 @@
         <v>1</v>
       </c>
       <c r="J187" t="n">
-        <v>6216.54</v>
+        <v>1078.58</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
@@ -10535,12 +10535,12 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ROLAMENTOS CBF LTDA.</t>
+          <t>LAPP BRASIL LTDA</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Misael Severino</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -10558,16 +10558,16 @@
         </is>
       </c>
       <c r="G188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J188" t="n">
-        <v>2741.75</v>
+        <v>25303.75</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -10582,19 +10582,19 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>1 de 1 entregas atrasadas</t>
+          <t>3 de 3 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RIBERMETALS COM IMP E EXP LTDA</t>
+          <t>ROLAMENTOS CBF LTDA.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Tatiana Carvalho de Souza</t>
+          <t>Misael Severino</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -10612,16 +10612,16 @@
         </is>
       </c>
       <c r="G189" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
       </c>
       <c r="I189" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J189" t="n">
-        <v>1309.51</v>
+        <v>2741.75</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
@@ -10636,14 +10636,14 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>3 de 3 entregas atrasadas</t>
+          <t>1 de 1 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>REWEFLON COMERCIAL LTDA</t>
+          <t>MURRELEKTRONIK DO BRASIL INDUSTRIA E COM</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -10666,16 +10666,16 @@
         </is>
       </c>
       <c r="G190" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
       </c>
       <c r="I190" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="J190" t="n">
-        <v>371.63</v>
+        <v>55415.2</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>1 de 1 entregas atrasadas</t>
+          <t>20 de 20 entregas atrasadas</t>
         </is>
       </c>
     </row>
@@ -10751,7 +10751,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>MURRELEKTRONIK DO BRASIL INDUSTRIA E COM</t>
+          <t>REWEFLON COMERCIAL LTDA</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -10774,16 +10774,16 @@
         </is>
       </c>
       <c r="G192" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
       </c>
       <c r="I192" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J192" t="n">
-        <v>55415.2</v>
+        <v>371.63</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
@@ -10798,19 +10798,19 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>20 de 20 entregas atrasadas</t>
+          <t>1 de 1 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TMF COMPONENTES ELETRO ELETRÔNICOS LTDA.</t>
+          <t>RIBERMETALS COM IMP E EXP LTDA</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Misael Severino</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -10837,7 +10837,7 @@
         <v>3</v>
       </c>
       <c r="J193" t="n">
-        <v>3845.86</v>
+        <v>1309.51</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
@@ -10859,12 +10859,12 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TRANSPACK INDUSTRIA E COMERCIO LTDA</t>
+          <t>SCHNEIDER ELECTRIC BRASIL LTDA</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Arthur Gabriel Dero</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -10891,7 +10891,7 @@
         <v>1</v>
       </c>
       <c r="J194" t="n">
-        <v>1319.2</v>
+        <v>6216.54</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
@@ -11021,12 +11021,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>USIFIL SERVICOS DE ELETROEROSAO A FIO LT</t>
+          <t>TMF COMPONENTES ELETRO ELETRÔNICOS LTDA.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Jair Wermuth</t>
+          <t>Misael Severino</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -11044,16 +11044,16 @@
         </is>
       </c>
       <c r="G197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
       </c>
       <c r="I197" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J197" t="n">
-        <v>8500</v>
+        <v>3845.86</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -11068,14 +11068,14 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>1 de 1 entregas atrasadas</t>
+          <t>3 de 3 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>TP2 IMPRESSOS E SERV DIGITAIS LTDA ME</t>
+          <t>VEDAX COMERCIAL LTDA.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11098,16 +11098,16 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J198" t="n">
-        <v>528</v>
+        <v>390.08</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
@@ -11122,29 +11122,29 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>1 de 1 entregas atrasadas</t>
+          <t>2 de 2 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>WEG EQUIPTOS ELETRICOS S/A.</t>
+          <t>TP2 IMPRESSOS E SERV DIGITAIS LTDA ME</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Misael Severino</t>
+          <t>Tatiana Carvalho de Souza</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="D199" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -11152,53 +11152,53 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H199" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I199" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J199" t="n">
-        <v>32960.32</v>
+        <v>528</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2 de 5 entregas atrasadas · 2 não conformidade(s)</t>
+          <t>1 de 1 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SMC AUTOMACAO DO BRASIL LTDA</t>
+          <t>TRANSPACK INDUSTRIA E COMERCIO LTDA</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Misael Severino</t>
+          <t>Arthur Gabriel Dero</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>0.2279569892473118</v>
+        <v>0.4</v>
       </c>
       <c r="D200" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E200" t="n">
-        <v>0.3799283154121864</v>
+        <v>0</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -11206,53 +11206,53 @@
         </is>
       </c>
       <c r="G200" t="n">
-        <v>279</v>
+        <v>1</v>
       </c>
       <c r="H200" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="I200" t="n">
-        <v>173</v>
+        <v>1</v>
       </c>
       <c r="J200" t="n">
-        <v>104019.34</v>
+        <v>1319.2</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M200" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>173 de 279 entregas atrasadas · 1 não conformidade(s)</t>
+          <t>1 de 1 entregas atrasadas</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SEW-EURODRIVE BRASIL LTDA</t>
+          <t>USIFIL SERVICOS DE ELETROEROSAO A FIO LT</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Misael Severino</t>
+          <t>Jair Wermuth</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4</v>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>0.2380952380952381</v>
+        <v>0</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -11260,31 +11260,31 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="H201" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I201" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="J201" t="n">
-        <v>77989.71000000001</v>
+        <v>8500</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
       <c r="L201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>16 de 21 entregas atrasadas · 1 não conformidade(s)</t>
+          <t>1 de 1 entregas atrasadas</t>
         </is>
       </c>
     </row>
